--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_225_R23.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_225_R23.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8969</v>
+        <v>8.109299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6666</v>
+        <v>8.610200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.5008</v>
       </c>
       <c r="G2" t="n">
         <v>4.9338</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8925</v>
+        <v>-0.68</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0455</v>
+        <v>-0.1019</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.847</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2256</v>
+        <v>5.1013</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6889</v>
+        <v>4.3966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5367</v>
+        <v>0.7047</v>
       </c>
       <c r="G3" t="n">
         <v>5.6653</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9063</v>
+        <v>-0.0305</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4481</v>
+        <v>0.2596</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4582</v>
+        <v>-0.2902</v>
       </c>
       <c r="V3" t="n">
         <v>0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1028</v>
+        <v>2.7553</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1903</v>
+        <v>3.0107</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-0.2555</v>
       </c>
       <c r="G4" t="n">
         <v>2.6583</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1224</v>
+        <v>-0.2251</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6869</v>
+        <v>0.5074</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5645</v>
+        <v>-0.7325</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2013</v>
+        <v>2.4633</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9737</v>
+        <v>2.1878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2275</v>
+        <v>0.2755</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2766</v>
+        <v>1.7763</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0086</v>
+        <v>-0.9842</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2681</v>
+        <v>2.7605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3353</v>
+        <v>1.9517</v>
       </c>
       <c r="K5" t="n">
-        <v>0.864</v>
+        <v>-0.5511</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5286999999999999</v>
+        <v>2.5027</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.612</v>
+        <v>-0.1754</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8726</v>
+        <v>-0.4331</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7393999999999999</v>
+        <v>0.2578</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>2.996</v>
+        <v>-0.0964</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3343</v>
+        <v>0.4681</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3383</v>
+        <v>-0.5645</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4455</v>
+        <v>1.6793</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8339</v>
+        <v>-0.2472</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6116</v>
+        <v>1.9265</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7763</v>
+        <v>0.8738</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9842</v>
+        <v>0.8704</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7605</v>
+        <v>0.0034</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9517</v>
+        <v>0.3022</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5511</v>
+        <v>0.9782</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5027</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1754</v>
+        <v>0.5715</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4331</v>
+        <v>-0.1078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2578</v>
+        <v>0.6793</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1142</v>
+        <v>-0.7795</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>0.1849</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2284</v>
+        <v>-0.9645</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0.4254</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0662</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8036</v>
+        <v>0.7327</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7374000000000001</v>
+        <v>0.2275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7094</v>
+        <v>-1.2766</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5426</v>
+        <v>-0.0086</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.2681</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0786</v>
+        <v>0.3353</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4367</v>
+        <v>0.864</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3581</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3692</v>
+        <v>-1.612</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8942</v>
+        <v>-0.8726</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4751</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0373</v>
+        <v>0.7549</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1889</v>
+        <v>1.0932</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1516</v>
+        <v>-0.3383</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0052</v>
+        <v>0.6623</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9549</v>
+        <v>1.5677</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9602</v>
+        <v>-0.9054</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8738</v>
+        <v>0.7094</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8704</v>
+        <v>1.5426</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0034</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3022</v>
+        <v>2.0786</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9782</v>
+        <v>2.4367</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.3581</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5715</v>
+        <v>-1.3692</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1078</v>
+        <v>-0.8942</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6793</v>
+        <v>-0.4751</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4536</v>
+        <v>-0.3666</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5228</v>
+        <v>-0.047</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.3196</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4254</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4254</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2182</v>
+        <v>0.539</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6394</v>
+        <v>-0.2855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4212</v>
+        <v>0.8245</v>
       </c>
       <c r="G9" t="n">
         <v>-0.021</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5709</v>
+        <v>-0.8138</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1845</v>
+        <v>0.1693</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3864</v>
+        <v>-0.9831</v>
       </c>
       <c r="V9" t="n">
         <v>0.6778999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5457</v>
+        <v>-1.4107</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8221</v>
+        <v>-1.5862</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2763</v>
+        <v>0.1755</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7026</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.539</v>
+        <v>-0.4039</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1656</v>
+        <v>-0.2664</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0378</v>
+        <v>-2.7175</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0568</v>
+        <v>-1.703</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9809</v>
+        <v>-1.0145</v>
       </c>
       <c r="G11" t="n">
         <v>-1.3759</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.198</v>
+        <v>-0.8777</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7499</v>
+        <v>-0.7835</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>2.5208</v>
       </c>
       <c r="I12" t="n">
-        <v>9.719999999999999</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>19.9637</v>
@@ -1390,16 +1390,16 @@
         <v>19.716</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.5188</v>
+        <v>-3.5186</v>
       </c>
       <c r="T12" t="n">
         <v>2.3019</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.820800000000001</v>
+        <v>-5.8207</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1417999999999997</v>
+        <v>0.1417999999999998</v>
       </c>
       <c r="W12" t="n">
         <v>4.856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0172</v>
+        <v>2.3038</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1292</v>
+        <v>1.4831</v>
       </c>
       <c r="F13" t="n">
-        <v>0.888</v>
+        <v>0.8207</v>
       </c>
       <c r="G13" t="n">
         <v>1.6965</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6071</v>
+        <v>-0.3205</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1494</v>
+        <v>0.2045</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4577</v>
+        <v>-0.525</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3261</v>
+        <v>1.9045</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6834</v>
+        <v>4.165</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3573</v>
+        <v>-2.2606</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3602</v>
+        <v>-0.3962</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3469</v>
+        <v>0.9255</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0133</v>
+        <v>-1.3217</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2624</v>
+        <v>2.5207</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4097</v>
+        <v>2.5242</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1472</v>
+        <v>-0.0035</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0978</v>
+        <v>-2.9169</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9373</v>
+        <v>-1.5987</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1605</v>
+        <v>-1.3182</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.2473</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>5.2558</v>
+        <v>-0.2201</v>
       </c>
       <c r="T14" t="n">
-        <v>5.3709</v>
+        <v>0.7472</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1151</v>
+        <v>-0.9673</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>3.2166</v>
       </c>
       <c r="W14" t="n">
-        <v>1.214</v>
+        <v>3.2166</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4561</v>
+        <v>0.5145</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9855</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5294</v>
+        <v>-0.3871</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3962</v>
+        <v>0.0113</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9255</v>
+        <v>-0.156</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3217</v>
+        <v>0.1673</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5207</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5242</v>
+        <v>0.0336</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0035</v>
+        <v>0.5889</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.9169</v>
+        <v>-0.6112</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5987</v>
+        <v>-0.1896</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3182</v>
+        <v>-0.4216</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6685</v>
+        <v>0.5032</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4323</v>
+        <v>0.2792</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2362</v>
+        <v>0.224</v>
       </c>
       <c r="V15" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0263</v>
+        <v>0.224</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5478</v>
+        <v>0.986</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5216</v>
+        <v>-0.762</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0113</v>
+        <v>-0.1561</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.156</v>
+        <v>-0.3301</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1673</v>
+        <v>0.174</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.0878</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0336</v>
+        <v>0.0707</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5889</v>
+        <v>1.0171</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6112</v>
+        <v>-1.2439</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1896</v>
+        <v>-0.4008</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4216</v>
+        <v>-0.8431</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0149</v>
+        <v>-0.174</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0747</v>
+        <v>-0.2436</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0896</v>
+        <v>0.0696</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2307</v>
+        <v>-0.2608</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6321</v>
+        <v>-0.8761</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8628</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1561</v>
+        <v>0.7968</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3301</v>
+        <v>-0.0263</v>
       </c>
       <c r="I17" t="n">
-        <v>0.174</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0878</v>
+        <v>0.3897</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0707</v>
+        <v>0.3529</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0171</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2439</v>
+        <v>0.4071</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4008</v>
+        <v>-0.3792</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8431</v>
+        <v>0.7863</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6286</v>
+        <v>-0.8257</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>-0.1061</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0312</v>
+        <v>-0.7196</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5132</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9941</v>
+        <v>-0.3922</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4809</v>
+        <v>-0.3321</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7968</v>
+        <v>-1.6821</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0263</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8231000000000001</v>
+        <v>-0.8298</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3897</v>
+        <v>-0.3452</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3529</v>
+        <v>-0.1478</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-0.1975</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4071</v>
+        <v>-1.3369</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3792</v>
+        <v>-0.7045</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7863</v>
+        <v>-0.6323</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.078</v>
+        <v>0.865</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>1.1127</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.854</v>
+        <v>-0.2478</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6969</v>
+        <v>-0.8149</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4865</v>
+        <v>2.3685</v>
       </c>
       <c r="F19" t="n">
         <v>-3.1834</v>
@@ -1936,10 +1936,10 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4075</v>
+        <v>1.2896</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2898</v>
+        <v>1.1718</v>
       </c>
       <c r="U19" t="n">
         <v>0.1177</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0947</v>
+        <v>-1.7064</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6281</v>
+        <v>-1.1474</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4665</v>
+        <v>-0.5589</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6821</v>
+        <v>-1.3602</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8522999999999999</v>
+        <v>-1.3469</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8298</v>
+        <v>-0.0133</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3452</v>
+        <v>-0.2624</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1478</v>
+        <v>-0.4097</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1975</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3369</v>
+        <v>-1.0978</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7045</v>
+        <v>-0.9373</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6323</v>
+        <v>-0.1605</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4946</v>
+        <v>2.2233</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8768</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3822</v>
+        <v>-0.3167</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7886</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7886</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8308</v>
+        <v>-3.5263</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8747</v>
+        <v>-2.167</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-1.3594</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2697</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4736</v>
+        <v>-0.1691</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9709</v>
+        <v>-0.2631</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4973</v>
+        <v>0.094</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3194</v>
+        <v>-4.2014</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1289</v>
+        <v>-1.011</v>
       </c>
       <c r="F22" t="n">
         <v>-3.1905</v>
@@ -2170,10 +2170,10 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7038</v>
+        <v>-0.5858</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U22" t="n">
         <v>-0.2557</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.5034</v>
+        <v>-5.6214</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2241</v>
+        <v>-2.3421</v>
       </c>
       <c r="F23" t="n">
         <v>-3.2793</v>
@@ -2248,10 +2248,10 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2582</v>
+        <v>1.1402</v>
       </c>
       <c r="T23" t="n">
-        <v>1.1404</v>
+        <v>1.0225</v>
       </c>
       <c r="U23" t="n">
         <v>0.1177</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7784</v>
+        <v>-6.2331</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0726</v>
+        <v>-3.4265</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7058</v>
+        <v>-2.8066</v>
       </c>
       <c r="G24" t="n">
         <v>-5.4717</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2473</v>
+        <v>-0.2074</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0395</v>
+        <v>-0.3143</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2078</v>
+        <v>0.107</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2383,7 +2383,7 @@
         <v>6.636299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0866</v>
+        <v>1.086599999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-19.9638</v>
@@ -2404,16 +2404,16 @@
         <v>10.4379</v>
       </c>
       <c r="S25" t="n">
-        <v>3.518699999999999</v>
+        <v>3.518700000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>5.820499999999999</v>
+        <v>5.8207</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.302</v>
+        <v>-2.3021</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1418000000000003</v>
+        <v>-0.1418000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>4.7142</v>
